--- a/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,86; 47,58</t>
+          <t>35,91; 47,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,99; 65,78</t>
+          <t>54,6; 65,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,48; 59,34</t>
+          <t>46,78; 59,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,77; 65,85</t>
+          <t>52,91; 66,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,36; 56,15</t>
+          <t>43,63; 56,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,14; 81,54</t>
+          <t>71,4; 82,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,12; 70,29</t>
+          <t>59,41; 70,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,09; 72,23</t>
+          <t>63,28; 72,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,5; 50,48</t>
+          <t>41,05; 49,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64,04; 72,12</t>
+          <t>63,73; 71,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,66; 63,25</t>
+          <t>54,2; 62,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,7; 67,91</t>
+          <t>59,69; 67,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,58; 44,64</t>
+          <t>36,27; 45,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,4; 55,59</t>
+          <t>46,4; 55,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,28; 60,59</t>
+          <t>51,11; 60,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,7; 38,14</t>
+          <t>27,72; 38,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,76; 64,25</t>
+          <t>55,86; 64,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,72; 72,55</t>
+          <t>64,12; 72,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,75; 74,07</t>
+          <t>65,73; 73,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,61; 42,06</t>
+          <t>33,97; 41,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,26; 53,47</t>
+          <t>46,98; 53,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56,54; 63,14</t>
+          <t>56,39; 62,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,03; 66,11</t>
+          <t>59,85; 66,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,06; 38,57</t>
+          <t>32,13; 38,92</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,41; 49,24</t>
+          <t>38,46; 49,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,52; 63,86</t>
+          <t>53,26; 64,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 56,36</t>
+          <t>45,87; 56,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,78; 46,2</t>
+          <t>35,66; 45,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,03; 72,45</t>
+          <t>62,44; 72,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,8; 72,21</t>
+          <t>61,98; 72,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,64; 65,34</t>
+          <t>55,65; 65,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,57; 49,88</t>
+          <t>40,71; 49,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,92; 59,72</t>
+          <t>51,53; 59,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,55; 67,15</t>
+          <t>59,5; 66,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52,38; 59,93</t>
+          <t>52,27; 59,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,8; 46,53</t>
+          <t>39,08; 46,49</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,42; 56,25</t>
+          <t>45,14; 55,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,3; 62,4</t>
+          <t>51,8; 61,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,54; 60,96</t>
+          <t>50,19; 60,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,28; 48,07</t>
+          <t>34,22; 47,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,24; 73,71</t>
+          <t>63,69; 73,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,31; 74,52</t>
+          <t>65,18; 74,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,89; 74,74</t>
+          <t>64,78; 74,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,3; 48,88</t>
+          <t>23,13; 49,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,38; 63,42</t>
+          <t>56,21; 63,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,8; 66,73</t>
+          <t>60,1; 66,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,99; 66,52</t>
+          <t>59,26; 66,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,29; 45,92</t>
+          <t>28,19; 45,87</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,11; 50,99</t>
+          <t>36,75; 50,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,79; 60,72</t>
+          <t>45,82; 60,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,01; 58,1</t>
+          <t>43,75; 57,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,35</t>
+          <t>6,88; 14,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,2; 64,1</t>
+          <t>50,68; 64,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,26; 84,68</t>
+          <t>73,8; 84,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,13; 66,6</t>
+          <t>53,77; 66,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 13,1</t>
+          <t>5,06; 12,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45,57; 55,73</t>
+          <t>45,07; 54,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,47; 71,47</t>
+          <t>62,05; 71,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,36; 60,77</t>
+          <t>51,36; 60,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,43</t>
+          <t>6,83; 12,23</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,03; 56,15</t>
+          <t>44,07; 56,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56,41; 68,86</t>
+          <t>56,1; 68,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,6; 51,21</t>
+          <t>38,57; 50,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44,15; 55,27</t>
+          <t>43,7; 54,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57,62; 69,43</t>
+          <t>57,75; 69,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,84; 81,75</t>
+          <t>71,85; 81,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,31; 62,58</t>
+          <t>50,96; 63,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,74; 55,96</t>
+          <t>46,3; 56,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,1; 61,32</t>
+          <t>52,93; 61,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65,97; 73,77</t>
+          <t>66,08; 73,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46,58; 55,54</t>
+          <t>46,01; 54,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,48; 53,79</t>
+          <t>46,86; 53,58</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,18; 45,12</t>
+          <t>36,91; 44,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,25; 61,59</t>
+          <t>52,81; 61,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,49; 46,88</t>
+          <t>37,47; 45,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,39; 26,16</t>
+          <t>18,74; 26,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,53; 62,18</t>
+          <t>54,35; 62,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,52; 71,42</t>
+          <t>63,73; 70,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,07; 57,96</t>
+          <t>50,22; 58,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,77; 68,77</t>
+          <t>25,83; 72,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46,97; 52,84</t>
+          <t>47,15; 52,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,92; 65,36</t>
+          <t>60,09; 65,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45,53; 51,42</t>
+          <t>45,78; 51,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,79; 60,26</t>
+          <t>23,71; 57,96</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,81; 50,26</t>
+          <t>42,36; 49,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,19; 47,87</t>
+          <t>40,28; 47,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,78; 51,91</t>
+          <t>44,37; 51,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,71; 30,84</t>
+          <t>9,45; 31,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,2; 62,13</t>
+          <t>55,19; 62,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,99; 59,97</t>
+          <t>52,75; 59,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,22; 62,09</t>
+          <t>55,22; 62,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,46; 44,51</t>
+          <t>38,3; 44,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49,84; 55,17</t>
+          <t>49,99; 55,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,88; 52,89</t>
+          <t>47,69; 52,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51,29; 56,4</t>
+          <t>50,94; 56,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,76; 36,55</t>
+          <t>18,39; 36,4</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42,58; 46,34</t>
+          <t>42,58; 46,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52,23; 55,7</t>
+          <t>52,17; 55,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47,97; 51,55</t>
+          <t>48,0; 51,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,38; 35,18</t>
+          <t>24,61; 35,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58,74; 62,17</t>
+          <t>58,8; 62,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,95; 69,23</t>
+          <t>65,88; 69,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,63; 62,93</t>
+          <t>59,8; 62,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38,18; 53,57</t>
+          <t>38,04; 53,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,27; 53,79</t>
+          <t>51,26; 53,76</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59,7; 62,11</t>
+          <t>59,72; 62,11</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54,38; 56,82</t>
+          <t>54,42; 56,76</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33,68; 42,82</t>
+          <t>33,86; 42,62</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97891; 129902</t>
+          <t>98048; 130844</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>159136; 193869</t>
+          <t>160936; 193343</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139471; 174308</t>
+          <t>137414; 174294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164354; 205076</t>
+          <t>164792; 206038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>113091; 146452</t>
+          <t>113793; 147027</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>204358; 234224</t>
+          <t>205094; 235582</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>170673; 202937</t>
+          <t>171528; 202710</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>182743; 209199</t>
+          <t>183279; 210217</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>221538; 269480</t>
+          <t>219135; 266011</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>372712; 419738</t>
+          <t>370927; 418244</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>318387; 368408</t>
+          <t>315717; 366845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>358868; 408184</t>
+          <t>358802; 406616</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>175421; 220091</t>
+          <t>178836; 223183</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>234562; 281011</t>
+          <t>234589; 281180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>257737; 304487</t>
+          <t>256881; 303372</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143613; 197718</t>
+          <t>143685; 197447</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>281009; 323773</t>
+          <t>281513; 327518</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>333722; 379976</t>
+          <t>335842; 378506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>343945; 387447</t>
+          <t>343848; 386303</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>178220; 216602</t>
+          <t>174942; 214312</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>471239; 533153</t>
+          <t>468420; 533059</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>581933; 649922</t>
+          <t>580403; 644108</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>615659; 678078</t>
+          <t>613839; 677523</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>331320; 398531</t>
+          <t>332070; 402171</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>122454; 156988</t>
+          <t>122627; 157876</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>170177; 206939</t>
+          <t>172589; 208073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147211; 179554</t>
+          <t>146114; 181318</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109918; 146020</t>
+          <t>112697; 145188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>208071; 243022</t>
+          <t>209430; 244323</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>210736; 246257</t>
+          <t>211368; 248456</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>183767; 219750</t>
+          <t>187161; 221300</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>141657; 174152</t>
+          <t>142142; 172811</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>339695; 390733</t>
+          <t>337171; 391111</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>396067; 446609</t>
+          <t>395711; 444298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>343050; 392438</t>
+          <t>342279; 389894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>264774; 309481</t>
+          <t>259929; 309209</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>162902; 201761</t>
+          <t>161889; 198512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>191847; 233370</t>
+          <t>193709; 231754</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>186970; 225539</t>
+          <t>185700; 224793</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107130; 150249</t>
+          <t>106942; 147254</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>238612; 273807</t>
+          <t>236573; 272937</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>254013; 289851</t>
+          <t>253520; 291486</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>251307; 289436</t>
+          <t>250877; 287028</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110863; 232528</t>
+          <t>110053; 233090</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>411623; 463053</t>
+          <t>410392; 462405</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>456220; 509140</t>
+          <t>458551; 510595</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>446713; 503714</t>
+          <t>448734; 503208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>230917; 361996</t>
+          <t>222189; 361616</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>75441; 103660</t>
+          <t>74721; 102903</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99494; 129092</t>
+          <t>97426; 128385</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92956; 122729</t>
+          <t>92406; 120901</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12381; 25656</t>
+          <t>12293; 25415</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>104256; 133115</t>
+          <t>105247; 133896</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>163068; 185959</t>
+          <t>162059; 186048</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>118319; 145573</t>
+          <t>117534; 146242</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13441; 33888</t>
+          <t>13086; 33098</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>187282; 229025</t>
+          <t>185234; 225779</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>269995; 308914</t>
+          <t>268176; 308902</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220743; 261206</t>
+          <t>220741; 262073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29383; 54364</t>
+          <t>29880; 53504</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>119235; 152051</t>
+          <t>119347; 152603</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>154564; 188653</t>
+          <t>153701; 186613</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>101557; 134735</t>
+          <t>101498; 133911</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119052; 149022</t>
+          <t>117824; 148052</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>160263; 193119</t>
+          <t>160625; 193255</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>201188; 228922</t>
+          <t>201207; 229515</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>137413; 170916</t>
+          <t>139174; 173037</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>117580; 143843</t>
+          <t>119026; 143983</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>291475; 336627</t>
+          <t>290538; 336385</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>365467; 408690</t>
+          <t>366084; 409050</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>249794; 297837</t>
+          <t>246733; 294053</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>244825; 283332</t>
+          <t>246785; 282182</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>228637; 277505</t>
+          <t>227023; 275491</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>352959; 408180</t>
+          <t>350010; 406386</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>252682; 307767</t>
+          <t>245989; 301781</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114802; 163293</t>
+          <t>117006; 164795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>348034; 396846</t>
+          <t>346889; 396031</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>440731; 495517</t>
+          <t>442226; 492434</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>346099; 400708</t>
+          <t>347160; 401747</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>218874; 584021</t>
+          <t>219390; 616480</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>588644; 662222</t>
+          <t>590911; 662330</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>812943; 886765</t>
+          <t>815230; 885339</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>613673; 693058</t>
+          <t>617052; 692195</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>350593; 887919</t>
+          <t>349389; 854127</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>318452; 373809</t>
+          <t>315060; 369892</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>313085; 372924</t>
+          <t>313803; 369708</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>348685; 404140</t>
+          <t>345437; 403384</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>90207; 286428</t>
+          <t>87766; 287957</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>432516; 486788</t>
+          <t>432443; 486517</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>436553; 494105</t>
+          <t>434555; 494178</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>456241; 512974</t>
+          <t>456222; 515466</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>276022; 319476</t>
+          <t>274894; 318720</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>761193; 842618</t>
+          <t>763445; 840115</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>767422; 847853</t>
+          <t>764404; 847344</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>823145; 905048</t>
+          <t>817486; 899358</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>308869; 601739</t>
+          <t>302808; 599254</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1395018; 1518207</t>
+          <t>1395138; 1511228</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1789667; 1908688</t>
+          <t>1787734; 1905940</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1628133; 1749665</t>
+          <t>1629433; 1743343</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>878030; 1217031</t>
+          <t>851461; 1212100</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1984896; 2100982</t>
+          <t>1987034; 2098254</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2346785; 2463521</t>
+          <t>2344188; 2461200</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2113439; 2230684</t>
+          <t>2119804; 2232713</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1417449; 1988813</t>
+          <t>1412102; 1968520</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3412677; 3580049</t>
+          <t>3411780; 3578155</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4170243; 4338258</t>
+          <t>4171772; 4338291</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3773554; 3942718</t>
+          <t>3775991; 3938798</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2415351; 3070970</t>
+          <t>2428411; 3056824</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,91; 47,93</t>
+          <t>36,27; 48,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,6; 65,6</t>
+          <t>54,11; 65,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,78; 59,33</t>
+          <t>46,29; 58,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,91; 66,16</t>
+          <t>50,16; 61,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,63; 56,37</t>
+          <t>43,53; 56,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,4; 82,01</t>
+          <t>71,81; 82,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,41; 70,21</t>
+          <t>59,56; 70,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,28; 72,58</t>
+          <t>59,41; 68,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,05; 49,83</t>
+          <t>41,34; 49,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63,73; 71,87</t>
+          <t>64,35; 72,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,2; 62,98</t>
+          <t>54,7; 63,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,69; 67,65</t>
+          <t>56,21; 63,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,27; 45,26</t>
+          <t>36,02; 44,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,4; 55,62</t>
+          <t>46,77; 55,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,11; 60,36</t>
+          <t>51,52; 60,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,72; 38,09</t>
+          <t>28,01; 37,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,86; 64,99</t>
+          <t>55,36; 64,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,12; 72,27</t>
+          <t>64,09; 72,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,73; 73,85</t>
+          <t>65,67; 73,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,97; 41,62</t>
+          <t>33,66; 40,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,98; 53,47</t>
+          <t>47,15; 53,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56,39; 62,58</t>
+          <t>56,65; 63,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59,85; 66,06</t>
+          <t>60,1; 66,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,13; 38,92</t>
+          <t>31,98; 37,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,46; 49,51</t>
+          <t>37,64; 49,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,26; 64,21</t>
+          <t>53,58; 64,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,87; 56,92</t>
+          <t>45,94; 56,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,66; 45,94</t>
+          <t>34,83; 45,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,44; 72,84</t>
+          <t>62,24; 72,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,98; 72,86</t>
+          <t>61,47; 72,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,65; 65,8</t>
+          <t>55,56; 66,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,71; 49,5</t>
+          <t>40,01; 49,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,53; 59,78</t>
+          <t>51,87; 59,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,5; 66,81</t>
+          <t>59,49; 67,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52,27; 59,54</t>
+          <t>52,15; 59,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,08; 46,49</t>
+          <t>39,43; 46,17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,14; 55,35</t>
+          <t>45,17; 55,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,8; 61,97</t>
+          <t>51,52; 61,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,19; 60,76</t>
+          <t>50,55; 60,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 47,11</t>
+          <t>33,87; 46,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,69; 73,48</t>
+          <t>64,06; 73,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,18; 74,94</t>
+          <t>65,18; 74,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,78; 74,11</t>
+          <t>65,04; 74,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,13; 49,0</t>
+          <t>43,69; 53,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,21; 63,33</t>
+          <t>56,22; 63,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,1; 66,93</t>
+          <t>59,92; 66,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59,26; 66,45</t>
+          <t>59,28; 66,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 45,87</t>
+          <t>40,46; 48,69</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,75; 50,61</t>
+          <t>37,06; 51,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,82; 60,38</t>
+          <t>46,31; 60,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,75; 57,24</t>
+          <t>44,45; 58,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 14,22</t>
+          <t>6,55; 13,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,68; 64,48</t>
+          <t>50,57; 64,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,8; 84,72</t>
+          <t>73,39; 84,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,77; 66,9</t>
+          <t>53,89; 66,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 12,79</t>
+          <t>9,14; 14,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45,07; 54,94</t>
+          <t>45,08; 55,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,05; 71,47</t>
+          <t>62,05; 71,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,36; 60,97</t>
+          <t>50,6; 60,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 12,23</t>
+          <t>8,47; 12,86</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,07; 56,35</t>
+          <t>44,12; 55,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56,1; 68,11</t>
+          <t>57,07; 69,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,57; 50,89</t>
+          <t>38,48; 50,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,7; 54,91</t>
+          <t>44,37; 54,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57,75; 69,48</t>
+          <t>57,75; 69,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,85; 81,96</t>
+          <t>71,53; 81,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,96; 63,36</t>
+          <t>50,13; 61,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,3; 56,01</t>
+          <t>45,4; 55,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,93; 61,28</t>
+          <t>52,76; 61,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,08; 73,83</t>
+          <t>65,34; 73,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46,01; 54,84</t>
+          <t>46,39; 55,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,86; 53,58</t>
+          <t>46,09; 53,68</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,91; 44,79</t>
+          <t>36,67; 44,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,81; 61,31</t>
+          <t>53,26; 61,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,47; 45,96</t>
+          <t>38,44; 46,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,74; 26,4</t>
+          <t>18,06; 24,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,35; 62,05</t>
+          <t>54,4; 62,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,73; 70,97</t>
+          <t>64,13; 71,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,22; 58,12</t>
+          <t>49,97; 57,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,83; 72,59</t>
+          <t>24,55; 30,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,15; 52,85</t>
+          <t>47,07; 52,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60,09; 65,26</t>
+          <t>59,89; 64,99</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45,78; 51,36</t>
+          <t>45,53; 51,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,71; 57,96</t>
+          <t>22,13; 26,55</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,36; 49,73</t>
+          <t>42,38; 49,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,28; 47,45</t>
+          <t>39,9; 47,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,37; 51,81</t>
+          <t>44,43; 52,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,45; 31,01</t>
+          <t>25,75; 32,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,19; 62,09</t>
+          <t>54,58; 61,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,75; 59,98</t>
+          <t>53,2; 60,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,22; 62,39</t>
+          <t>55,18; 62,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,3; 44,41</t>
+          <t>38,04; 43,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49,99; 55,01</t>
+          <t>49,68; 54,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,69; 52,86</t>
+          <t>47,84; 52,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50,94; 56,04</t>
+          <t>51,12; 55,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,39; 36,4</t>
+          <t>32,94; 37,49</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42,58; 46,12</t>
+          <t>42,75; 46,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52,17; 55,62</t>
+          <t>51,99; 55,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48,0; 51,36</t>
+          <t>47,85; 51,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,61; 35,03</t>
+          <t>31,32; 34,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58,8; 62,09</t>
+          <t>58,68; 61,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,88; 69,17</t>
+          <t>65,86; 69,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,8; 62,99</t>
+          <t>59,57; 62,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38,04; 53,03</t>
+          <t>38,36; 41,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,26; 53,76</t>
+          <t>51,31; 53,76</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59,72; 62,11</t>
+          <t>59,62; 62,05</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54,42; 56,76</t>
+          <t>54,43; 56,78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33,86; 42,62</t>
+          <t>35,31; 37,64</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184716</t>
+          <t>177274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>197039</t>
+          <t>203243</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>381755</t>
+          <t>380516</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98048; 130844</t>
+          <t>99013; 131168</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>160936; 193343</t>
+          <t>159471; 193501</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>137414; 174294</t>
+          <t>135974; 173052</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164792; 206038</t>
+          <t>159934; 195254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>113793; 147027</t>
+          <t>113554; 146234</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>205094; 235582</t>
+          <t>206266; 235848</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>171528; 202710</t>
+          <t>171944; 204158</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>183279; 210217</t>
+          <t>187776; 217004</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>219135; 266011</t>
+          <t>220676; 266582</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>370927; 418244</t>
+          <t>374488; 419374</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>315717; 366845</t>
+          <t>318597; 368022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>358802; 406616</t>
+          <t>356867; 404847</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>170404</t>
+          <t>172135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>195407</t>
+          <t>203506</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>365811</t>
+          <t>375641</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>178836; 223183</t>
+          <t>177599; 221323</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>234589; 281180</t>
+          <t>236412; 280322</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>256881; 303372</t>
+          <t>258947; 303705</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143685; 197447</t>
+          <t>148659; 199168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>281513; 327518</t>
+          <t>278982; 324103</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>335842; 378506</t>
+          <t>335706; 378678</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>343848; 386303</t>
+          <t>343526; 386116</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>174942; 214312</t>
+          <t>183957; 223089</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>468420; 533059</t>
+          <t>470117; 534657</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>580403; 644108</t>
+          <t>583105; 650586</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>613839; 677523</t>
+          <t>616437; 679428</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>332070; 402171</t>
+          <t>344523; 408543</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128591</t>
+          <t>126420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>157502</t>
+          <t>159441</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>286093</t>
+          <t>285861</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>122627; 157876</t>
+          <t>120010; 157221</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172589; 208073</t>
+          <t>173621; 209525</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146114; 181318</t>
+          <t>146343; 180216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112697; 145188</t>
+          <t>110069; 143034</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>209430; 244323</t>
+          <t>208748; 243502</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>211368; 248456</t>
+          <t>209636; 245708</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>187161; 221300</t>
+          <t>186838; 223169</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>142142; 172811</t>
+          <t>142577; 175164</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>337171; 391111</t>
+          <t>339376; 389623</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>395711; 444298</t>
+          <t>395615; 445688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>342279; 389894</t>
+          <t>341512; 392278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>259929; 309209</t>
+          <t>265133; 310433</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127957</t>
+          <t>150417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>183799</t>
+          <t>206057</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>311756</t>
+          <t>356474</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>161889; 198512</t>
+          <t>162020; 198916</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>193709; 231754</t>
+          <t>192681; 231561</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>185700; 224793</t>
+          <t>187017; 225471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>106942; 147254</t>
+          <t>126370; 172590</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>236573; 272937</t>
+          <t>237971; 271646</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>253520; 291486</t>
+          <t>253503; 289113</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>250877; 287028</t>
+          <t>251887; 288242</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110053; 233090</t>
+          <t>184353; 226585</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>410392; 462405</t>
+          <t>410455; 462689</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>458551; 510595</t>
+          <t>457126; 510640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>448734; 503208</t>
+          <t>448929; 503189</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>222189; 361616</t>
+          <t>321740; 387112</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>45815</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>74721; 102903</t>
+          <t>75346; 104013</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97426; 128385</t>
+          <t>98473; 128525</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92406; 120901</t>
+          <t>93884; 123626</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12293; 25415</t>
+          <t>13480; 27111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>105247; 133896</t>
+          <t>105012; 133429</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>162059; 186048</t>
+          <t>161149; 185719</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>117534; 146242</t>
+          <t>117792; 145431</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13086; 33098</t>
+          <t>20923; 33507</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>185234; 225779</t>
+          <t>185280; 227784</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>268176; 308902</t>
+          <t>268175; 308451</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220741; 262073</t>
+          <t>217500; 258367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29880; 53504</t>
+          <t>36804; 55871</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133351</t>
+          <t>133669</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>130596</t>
+          <t>132457</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>263947</t>
+          <t>266126</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>119347; 152603</t>
+          <t>119473; 151274</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>153701; 186613</t>
+          <t>156361; 190032</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>101498; 133911</t>
+          <t>101261; 133987</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>117824; 148052</t>
+          <t>120117; 147937</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>160625; 193255</t>
+          <t>160624; 192178</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>201207; 229515</t>
+          <t>200317; 229314</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>139174; 173037</t>
+          <t>136918; 168805</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>119026; 143983</t>
+          <t>119734; 146349</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>290538; 336385</t>
+          <t>289610; 336311</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>366084; 409050</t>
+          <t>362002; 407833</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246733; 294053</t>
+          <t>248761; 295660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>246785; 282182</t>
+          <t>246350; 286882</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137359</t>
+          <t>152527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>378430</t>
+          <t>211479</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>515789</t>
+          <t>364006</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>227023; 275491</t>
+          <t>225560; 276041</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>350010; 406386</t>
+          <t>352999; 408167</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>245989; 301781</t>
+          <t>252393; 305709</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117006; 164795</t>
+          <t>129972; 177661</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>346889; 396031</t>
+          <t>347188; 397362</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>442226; 492434</t>
+          <t>444989; 496407</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>347160; 401747</t>
+          <t>345465; 399130</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>219390; 616480</t>
+          <t>189540; 236445</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>590911; 662330</t>
+          <t>589944; 660778</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>815230; 885339</t>
+          <t>812521; 881626</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>617052; 692195</t>
+          <t>613730; 688245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>349389; 854127</t>
+          <t>330080; 396055</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>204313</t>
+          <t>230422</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>297225</t>
+          <t>340661</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>501538</t>
+          <t>571084</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>315060; 369892</t>
+          <t>315255; 371787</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>313803; 369708</t>
+          <t>310870; 369281</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>345437; 403384</t>
+          <t>345941; 404914</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>87766; 287957</t>
+          <t>205488; 257437</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>432443; 486517</t>
+          <t>427647; 484233</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>434555; 494178</t>
+          <t>438325; 496222</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>456222; 515466</t>
+          <t>455912; 515703</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>274894; 318720</t>
+          <t>316226; 364866</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>763445; 840115</t>
+          <t>758697; 838291</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>764404; 847344</t>
+          <t>766830; 844892</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>817486; 899358</t>
+          <t>820305; 897433</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>302808; 599254</t>
+          <t>536779; 610823</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1104702</t>
+          <t>1162000</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1564793</t>
+          <t>1483525</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2669494</t>
+          <t>2645524</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1395138; 1511228</t>
+          <t>1400719; 1511926</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1787734; 1905940</t>
+          <t>1781529; 1911230</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1629433; 1743343</t>
+          <t>1624172; 1744035</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>851461; 1212100</t>
+          <t>1106345; 1221352</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1987034; 2098254</t>
+          <t>1983020; 2093417</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2344188; 2461200</t>
+          <t>2343467; 2459148</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2119804; 2232713</t>
+          <t>2111362; 2229526</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1412102; 1968520</t>
+          <t>1433536; 1533086</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3411780; 3578155</t>
+          <t>3414949; 3578136</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4171772; 4338291</t>
+          <t>4164479; 4334381</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3775991; 3938798</t>
+          <t>3777097; 3939736</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2428411; 3056824</t>
+          <t>2567115; 2736520</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
